--- a/data/trans_orig/DC_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58459</t>
+          <t>58612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98273</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>82763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>139522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341524</t>
+          <t>344481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384060</t>
+          <t>384478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214927</t>
+          <t>215699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254741</t>
+          <t>254588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574005</t>
+          <t>573665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>632625</t>
+          <t>630424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64971</t>
+          <t>64169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128688</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312893</t>
+          <t>322204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167676</t>
+          <t>170030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406140</t>
+          <t>409408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358576</t>
+          <t>359378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391414</t>
+          <t>390741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199200</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383405</t>
+          <t>379964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>529500</t>
+          <t>526232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>767964</t>
+          <t>765610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70803</t>
+          <t>69134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108291</t>
+          <t>106263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130681</t>
+          <t>126323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196303</t>
+          <t>194608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216069</t>
+          <t>218364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286190</t>
+          <t>283737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428047</t>
+          <t>430075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465535</t>
+          <t>467204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>395699</t>
+          <t>397394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461321</t>
+          <t>465679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842150</t>
+          <t>844603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>912271</t>
+          <t>909976</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68771</t>
+          <t>71450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>236125</t>
+          <t>238114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219461</t>
+          <t>225560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286364</t>
+          <t>288326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246106</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>516591</t>
+          <t>521243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>651661</t>
+          <t>649672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>819015</t>
+          <t>816336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426517</t>
+          <t>424555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493420</t>
+          <t>487321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1084076</t>
+          <t>1079424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1354561</t>
+          <t>1331598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151253</t>
+          <t>154190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193898</t>
+          <t>195312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234158</t>
+          <t>235573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268790</t>
+          <t>269643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397035</t>
+          <t>397704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453118</t>
+          <t>453083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367336</t>
+          <t>365922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409981</t>
+          <t>407044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>279115</t>
+          <t>278262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313747</t>
+          <t>312332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656021</t>
+          <t>656056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>712104</t>
+          <t>711435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133080</t>
+          <t>133128</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>301386</t>
+          <t>300536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>522675</t>
+          <t>518053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>402129</t>
+          <t>402547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>732950</t>
+          <t>739175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235085</t>
+          <t>235037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263618</t>
+          <t>263934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85693</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306982</t>
+          <t>307832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243583</t>
+          <t>237358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>574404</t>
+          <t>573986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115801</t>
+          <t>114641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140976</t>
+          <t>140247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259237</t>
+          <t>260250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288732</t>
+          <t>287859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>381476</t>
+          <t>381785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>420286</t>
+          <t>419730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141783</t>
+          <t>142512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166958</t>
+          <t>168118</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137099</t>
+          <t>137972</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166594</t>
+          <t>165581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>288304</t>
+          <t>288860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>327114</t>
+          <t>326805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>593275</t>
+          <t>570239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>826212</t>
+          <t>823821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1469461</t>
+          <t>1468343</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2013722</t>
+          <t>2005111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2139444</t>
+          <t>2157419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2875621</t>
+          <t>2827859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2633605</t>
+          <t>2635996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2866542</t>
+          <t>2889578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1698558</t>
+          <t>1707169</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2242819</t>
+          <t>2243937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4296476</t>
+          <t>4344238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5032653</t>
+          <t>5014678</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76671</t>
+          <t>90990</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58612</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97501</t>
+          <t>116661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>107961</t>
+          <t>124324</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82763</t>
+          <t>97055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139522</t>
+          <t>161863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>368696</t>
+          <t>374459</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>344481</t>
+          <t>350823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384478</t>
+          <t>389862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236529</t>
+          <t>271522</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215699</t>
+          <t>245851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254588</t>
+          <t>294319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>605226</t>
+          <t>645981</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573665</t>
+          <t>608442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630424</t>
+          <t>673250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45953</t>
+          <t>51592</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>36938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64169</t>
+          <t>71010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>129334</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>109569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322204</t>
+          <t>150610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>234121</t>
+          <t>180925</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170030</t>
+          <t>153091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>409408</t>
+          <t>207879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>425298</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359378</t>
+          <t>405880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390741</t>
+          <t>439952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>323925</t>
+          <t>372399</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>351123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379964</t>
+          <t>392164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>701519</t>
+          <t>797698</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>526232</t>
+          <t>770744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765610</t>
+          <t>825532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86562</t>
+          <t>95548</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69134</t>
+          <t>77569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106263</t>
+          <t>115383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>170884</t>
+          <t>198565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126323</t>
+          <t>178297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194608</t>
+          <t>218948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257446</t>
+          <t>294113</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218364</t>
+          <t>268629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283737</t>
+          <t>322748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>449776</t>
+          <t>525289</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430075</t>
+          <t>505454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467204</t>
+          <t>543268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>421118</t>
+          <t>424628</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>397394</t>
+          <t>404245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465679</t>
+          <t>444896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>870894</t>
+          <t>949916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>844603</t>
+          <t>921281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>909976</t>
+          <t>975400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>163566</t>
+          <t>174398</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238114</t>
+          <t>200176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>261928</t>
+          <t>286077</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225560</t>
+          <t>266027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288326</t>
+          <t>308436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>425494</t>
+          <t>460476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>430058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>521243</t>
+          <t>493746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>724220</t>
+          <t>526219</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>649672</t>
+          <t>500441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>816336</t>
+          <t>549620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>450953</t>
+          <t>450809</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424555</t>
+          <t>428450</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487321</t>
+          <t>470859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1175173</t>
+          <t>977028</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1079424</t>
+          <t>943758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1331598</t>
+          <t>1007446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>173923</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154190</t>
+          <t>164262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195312</t>
+          <t>207191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>252420</t>
+          <t>281751</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235573</t>
+          <t>263869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>269643</t>
+          <t>300951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>426343</t>
+          <t>466087</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397704</t>
+          <t>436521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453083</t>
+          <t>495561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>387311</t>
+          <t>425011</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365922</t>
+          <t>402155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407044</t>
+          <t>445084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>295485</t>
+          <t>327104</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278262</t>
+          <t>307904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312332</t>
+          <t>344986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>682796</t>
+          <t>752115</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656056</t>
+          <t>722641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>711435</t>
+          <t>781681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,17%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>118499</t>
+          <t>129407</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104231</t>
+          <t>113672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133128</t>
+          <t>146085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>409189</t>
+          <t>227018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300536</t>
+          <t>212818</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>518053</t>
+          <t>242717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>527688</t>
+          <t>356425</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>402547</t>
+          <t>334623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>739175</t>
+          <t>379956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>249666</t>
+          <t>277673</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235037</t>
+          <t>260995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263934</t>
+          <t>293408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>199179</t>
+          <t>212148</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>196449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>307832</t>
+          <t>226348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>448845</t>
+          <t>489821</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237358</t>
+          <t>466290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>573986</t>
+          <t>511623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>127804</t>
+          <t>140620</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114641</t>
+          <t>126042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140247</t>
+          <t>154596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>274490</t>
+          <t>301626</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260250</t>
+          <t>285967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287859</t>
+          <t>315660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>402294</t>
+          <t>442247</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>381785</t>
+          <t>420346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>419730</t>
+          <t>462714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>154955</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142512</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168118</t>
+          <t>184156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>151341</t>
+          <t>162983</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137972</t>
+          <t>148949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165581</t>
+          <t>178642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>306296</t>
+          <t>332560</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>288860</t>
+          <t>312093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>326805</t>
+          <t>354461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>570239</t>
+          <t>759866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>823821</t>
+          <t>864592</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1468343</t>
+          <t>1464653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2005111</t>
+          <t>1567010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2157419</t>
+          <t>2244812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2827859</t>
+          <t>2402482</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2712220</t>
+          <t>2723527</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2635996</t>
+          <t>2668170</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2889578</t>
+          <t>2772896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2078530</t>
+          <t>2221592</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1707169</t>
+          <t>2169944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2243937</t>
+          <t>2272301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4790750</t>
+          <t>4945119</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4344238</t>
+          <t>4867234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5014678</t>
+          <t>5024904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
